--- a/samples/QC_Measurement_Tools_sample.xlsx
+++ b/samples/QC_Measurement_Tools_sample.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -53,11 +52,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -442,6 +443,7 @@
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,9 +527,14 @@
           <t>Tracking Number (Blank if as Recipient)</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Destination (Blank if as Recipient)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="4" t="n">
         <v>46041.42140046296</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -573,7 +580,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="5" t="n">
         <v>46041</v>
       </c>
       <c r="O2" t="inlineStr">
@@ -584,9 +591,14 @@
       <c r="P2" t="n">
         <v>736104</v>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Sidoarjo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="4" t="n">
         <v>46043.55703703704</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -632,12 +644,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="5" t="n">
         <v>46043</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="4" t="n">
         <v>46047.35423611111</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -683,7 +695,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="5" t="n">
         <v>46047</v>
       </c>
       <c r="O4" t="inlineStr">
@@ -694,9 +706,14 @@
       <c r="P4" t="n">
         <v>191326</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Bandung</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="4" t="n">
         <v>46050.33574074074</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -742,7 +759,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="5" t="n">
         <v>46050</v>
       </c>
       <c r="O5" t="inlineStr">
@@ -753,9 +770,14 @@
       <c r="P5" t="n">
         <v>701962</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="4" t="n">
         <v>46050.639375</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -801,12 +823,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="5" t="n">
         <v>46050</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="4" t="n">
         <v>46053.54693287037</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -862,7 +884,7 @@
           <t>https://drive.google.com/open?id=6JcbBNmG-kCaIUmFZc6o01DHygbBWA0sm</t>
         </is>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="5" t="n">
         <v>46053</v>
       </c>
       <c r="O7" t="inlineStr">
@@ -873,9 +895,14 @@
       <c r="P7" t="n">
         <v>825244</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Denpasar</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="4" t="n">
         <v>46053.56846064814</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -921,7 +948,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" s="5" t="n">
         <v>46053</v>
       </c>
       <c r="O8" t="inlineStr">
@@ -932,9 +959,14 @@
       <c r="P8" t="n">
         <v>736307</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Batam</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="4" t="n">
         <v>46055.53310185186</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,12 +1012,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" s="5" t="n">
         <v>46055</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="4" t="n">
         <v>46056.55329861111</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1031,12 +1063,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="5" t="n">
         <v>46056</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="4" t="n">
         <v>46057.38878472222</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1097,12 +1129,12 @@
           <t>https://drive.google.com/open?id=G9NoePPSfsNHm2qE3eKDHFRfRNLdzvUMU</t>
         </is>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="5" t="n">
         <v>46057</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="4" t="n">
         <v>46059.50682870371</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1148,7 +1180,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="5" t="n">
         <v>46059</v>
       </c>
       <c r="O12" t="inlineStr">
@@ -1159,9 +1191,14 @@
       <c r="P12" t="n">
         <v>272150</v>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Denpasar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="4" t="n">
         <v>46064.53429398148</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1207,12 +1244,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" s="5" t="n">
         <v>46064</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="4" t="n">
         <v>46076.66224537037</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1263,7 +1300,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="5" t="n">
         <v>46076</v>
       </c>
       <c r="O14" t="inlineStr">
@@ -1274,9 +1311,14 @@
       <c r="P14" t="n">
         <v>568043</v>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Lampung</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="4" t="n">
         <v>46078.62024305556</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1364,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="5" t="n">
         <v>46078</v>
       </c>
       <c r="O15" t="inlineStr">
@@ -1333,9 +1375,14 @@
       <c r="P15" t="n">
         <v>811392</v>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Cilegon</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="4" t="n">
         <v>46078.35547453703</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,12 +1428,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" s="5" t="n">
         <v>46078</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="4" t="n">
         <v>46080.57201388889</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1432,7 +1479,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" s="5" t="n">
         <v>46080</v>
       </c>
       <c r="O17" t="inlineStr">
@@ -1443,9 +1490,14 @@
       <c r="P17" t="n">
         <v>969322</v>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Sidoarjo</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="4" t="n">
         <v>46082.45381944445</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1491,12 +1543,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="5" t="n">
         <v>46082</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="4" t="n">
         <v>46085.38243055555</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1542,7 +1594,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="5" t="n">
         <v>46085</v>
       </c>
       <c r="O19" t="inlineStr">
@@ -1553,9 +1605,14 @@
       <c r="P19" t="n">
         <v>610400</v>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Cilegon</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="4" t="n">
         <v>46085.58986111111</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1601,12 +1658,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="5" t="n">
         <v>46085</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="4" t="n">
         <v>46086.69586805555</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1652,7 +1709,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="5" t="n">
         <v>46086</v>
       </c>
       <c r="O21" t="inlineStr">
@@ -1663,9 +1720,14 @@
       <c r="P21" t="n">
         <v>415651</v>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Cilegon</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="4" t="n">
         <v>46089.55599537037</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1711,12 +1773,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="5" t="n">
         <v>46089</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="4" t="n">
         <v>46089.49895833333</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1762,12 +1824,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N23" s="5" t="n">
         <v>46089</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="4" t="n">
         <v>46102.49303240741</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1823,7 +1885,7 @@
           <t>https://drive.google.com/open?id=4F0RlwoUSaXTzIWgVkZDBmpa9NV4GPgPj</t>
         </is>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" s="5" t="n">
         <v>46102</v>
       </c>
       <c r="O24" t="inlineStr">
@@ -1834,9 +1896,14 @@
       <c r="P24" t="n">
         <v>767345</v>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Gresik</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="4" t="n">
         <v>46103.36810185185</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1882,7 +1949,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" s="5" t="n">
         <v>46103</v>
       </c>
       <c r="O25" t="inlineStr">
@@ -1893,9 +1960,14 @@
       <c r="P25" t="n">
         <v>848739</v>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Gresik</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="4" t="n">
         <v>46105.62943287037</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1951,12 +2023,12 @@
           <t>https://drive.google.com/open?id=wDg9_WYCUtbgh3FswYOops6UvzcEWOdX7</t>
         </is>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="5" t="n">
         <v>46105</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="4" t="n">
         <v>46105.61269675926</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2002,12 +2074,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="5" t="n">
         <v>46105</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="4" t="n">
         <v>46107.64199074074</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2063,7 +2135,7 @@
           <t>https://drive.google.com/open?id=cww23fvdXa9pHkixtCjygCwJyMAOH6jbZ</t>
         </is>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" s="5" t="n">
         <v>46107</v>
       </c>
       <c r="O28" t="inlineStr">
@@ -2074,9 +2146,14 @@
       <c r="P28" t="n">
         <v>780737</v>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Cikarang</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="4" t="n">
         <v>46109.40155092593</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2122,7 +2199,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="5" t="n">
         <v>46109</v>
       </c>
       <c r="O29" t="inlineStr">
@@ -2133,9 +2210,14 @@
       <c r="P29" t="n">
         <v>819722</v>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="4" t="n">
         <v>46109.38407407407</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2181,12 +2263,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="N30" s="5" t="n">
         <v>46109</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="4" t="n">
         <v>46113.37030092593</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2232,12 +2314,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" s="5" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="4" t="n">
         <v>46119.38116898148</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2293,7 +2375,7 @@
           <t>https://drive.google.com/open?id=tQCvRuhviUhQ_gdjOkdhCBDtcDWpH892e</t>
         </is>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="5" t="n">
         <v>46119</v>
       </c>
       <c r="O32" t="inlineStr">
@@ -2304,9 +2386,14 @@
       <c r="P32" t="n">
         <v>595773</v>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Bandung</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="4" t="n">
         <v>46119.54479166667</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2362,7 +2449,7 @@
           <t>https://drive.google.com/open?id=YM02HQW-2WFirHUfpx48HUYN5IOffCN0g</t>
         </is>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="5" t="n">
         <v>46119</v>
       </c>
       <c r="O33" t="inlineStr">
@@ -2373,9 +2460,14 @@
       <c r="P33" t="n">
         <v>736198</v>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Denpasar</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="4" t="n">
         <v>46122.33549768518</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2431,12 +2523,12 @@
           <t>https://drive.google.com/open?id=tIx-ctZOYl7VS-KSYVl6gIUJNztFXWeU7</t>
         </is>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="5" t="n">
         <v>46122</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="4" t="n">
         <v>46122.63664351852</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2492,12 +2584,12 @@
           <t>https://drive.google.com/open?id=TPGXuaJy0rMmGZ89_RAYkYTTmLyh7nkMF</t>
         </is>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="N35" s="5" t="n">
         <v>46122</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="4" t="n">
         <v>46126.6883912037</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2553,7 +2645,7 @@
           <t>https://drive.google.com/open?id=Sp6LHkanipVgJya7umAq1ZLNzWMzAzT9a</t>
         </is>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="N36" s="5" t="n">
         <v>46126</v>
       </c>
       <c r="O36" t="inlineStr">
@@ -2564,9 +2656,14 @@
       <c r="P36" t="n">
         <v>807239</v>
       </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Jambi</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="4" t="n">
         <v>46131.34577546296</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2622,12 +2719,12 @@
           <t>https://drive.google.com/open?id=B_W2Fr6Qtv7AaopKerOaEhtc21yZnAkr3</t>
         </is>
       </c>
-      <c r="N37" s="3" t="n">
+      <c r="N37" s="5" t="n">
         <v>46131</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="4" t="n">
         <v>46141.38549768519</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2673,7 +2770,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="N38" s="5" t="n">
         <v>46141</v>
       </c>
       <c r="O38" t="inlineStr">
@@ -2684,9 +2781,14 @@
       <c r="P38" t="n">
         <v>190000</v>
       </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Sidoarjo</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="4" t="n">
         <v>46144.4287962963</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2732,7 +2834,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" s="5" t="n">
         <v>46144</v>
       </c>
       <c r="O39" t="inlineStr">
@@ -2743,9 +2845,14 @@
       <c r="P39" t="n">
         <v>504129</v>
       </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Kediri</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="4" t="n">
         <v>46145.5124537037</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2791,12 +2898,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="N40" s="5" t="n">
         <v>46145</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="4" t="n">
         <v>46147.60506944444</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2842,7 +2949,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="N41" s="5" t="n">
         <v>46147</v>
       </c>
       <c r="O41" t="inlineStr">
@@ -2853,9 +2960,14 @@
       <c r="P41" t="n">
         <v>322884</v>
       </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Medan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="4" t="n">
         <v>46147.66987268518</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2901,12 +3013,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="N42" s="5" t="n">
         <v>46147</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="4" t="n">
         <v>46149.37739583333</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2952,12 +3064,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" s="5" t="n">
         <v>46149</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="4" t="n">
         <v>46152.58576388889</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -3013,7 +3125,7 @@
           <t>https://drive.google.com/open?id=9LgItPCJQL-2LmkDUrT5NPt4AnwvTA88j</t>
         </is>
       </c>
-      <c r="N44" s="3" t="n">
+      <c r="N44" s="5" t="n">
         <v>46152</v>
       </c>
       <c r="O44" t="inlineStr">
@@ -3024,9 +3136,14 @@
       <c r="P44" t="n">
         <v>526250</v>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Cilegon</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="4" t="n">
         <v>46155.6247337963</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -3082,12 +3199,12 @@
           <t>https://drive.google.com/open?id=5idH8S-aFB3PvShi453EvNeDR0_LULgsJ</t>
         </is>
       </c>
-      <c r="N45" s="3" t="n">
+      <c r="N45" s="5" t="n">
         <v>46155</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="4" t="n">
         <v>46162.59806712963</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -3143,7 +3260,7 @@
           <t>https://drive.google.com/open?id=myAFBEZMSXt5TlNfRZj9HVockMc2Trsk4</t>
         </is>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="N46" s="5" t="n">
         <v>46162</v>
       </c>
       <c r="O46" t="inlineStr">
@@ -3154,9 +3271,14 @@
       <c r="P46" t="n">
         <v>794476</v>
       </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Cilegon</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="4" t="n">
         <v>46162.34422453704</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -3202,7 +3324,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N47" s="3" t="n">
+      <c r="N47" s="5" t="n">
         <v>46162</v>
       </c>
       <c r="O47" t="inlineStr">
@@ -3213,9 +3335,14 @@
       <c r="P47" t="n">
         <v>567051</v>
       </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Bandung</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="4" t="n">
         <v>46164.35787037037</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -3266,12 +3393,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N48" s="3" t="n">
+      <c r="N48" s="5" t="n">
         <v>46164</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="4" t="n">
         <v>46166.64827546296</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3332,12 +3459,12 @@
           <t>https://drive.google.com/open?id=0ybSmt4z9Y4W94CgZ_QIWSEMtOaYALYKq</t>
         </is>
       </c>
-      <c r="N49" s="3" t="n">
+      <c r="N49" s="5" t="n">
         <v>46166</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="4" t="n">
         <v>46167.59607638889</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3393,7 +3520,7 @@
           <t>https://drive.google.com/open?id=YikdqHYf59Xi5XlJEaQnZtZUBDcqLkKB1</t>
         </is>
       </c>
-      <c r="N50" s="3" t="n">
+      <c r="N50" s="5" t="n">
         <v>46167</v>
       </c>
       <c r="O50" t="inlineStr">
@@ -3404,9 +3531,14 @@
       <c r="P50" t="n">
         <v>476623</v>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Denpasar</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="4" t="n">
         <v>46169.34002314815</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3462,12 +3594,12 @@
           <t>https://drive.google.com/open?id=v5ohjnPWbuuP6pv0AskgNk91tEDALpWZ3</t>
         </is>
       </c>
-      <c r="N51" s="3" t="n">
+      <c r="N51" s="5" t="n">
         <v>46169</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="4" t="n">
         <v>46180.53931712963</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3513,7 +3645,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N52" s="3" t="n">
+      <c r="N52" s="5" t="n">
         <v>46180</v>
       </c>
       <c r="O52" t="inlineStr">
@@ -3524,9 +3656,14 @@
       <c r="P52" t="n">
         <v>784242</v>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Jambi</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="4" t="n">
         <v>46182.54232638889</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3572,12 +3709,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N53" s="3" t="n">
+      <c r="N53" s="5" t="n">
         <v>46182</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="4" t="n">
         <v>46185.61217592593</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3623,7 +3760,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N54" s="3" t="n">
+      <c r="N54" s="5" t="n">
         <v>46185</v>
       </c>
       <c r="O54" t="inlineStr">
@@ -3634,9 +3771,14 @@
       <c r="P54" t="n">
         <v>444909</v>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Kediri</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="4" t="n">
         <v>46190.61625</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3682,7 +3824,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N55" s="3" t="n">
+      <c r="N55" s="5" t="n">
         <v>46190</v>
       </c>
       <c r="O55" t="inlineStr">
@@ -3693,9 +3835,14 @@
       <c r="P55" t="n">
         <v>986159</v>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Gresik</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="4" t="n">
         <v>46190.42331018519</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3746,12 +3893,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N56" s="3" t="n">
+      <c r="N56" s="5" t="n">
         <v>46190</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="4" t="n">
         <v>46191.61833333333</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3797,7 +3944,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N57" s="3" t="n">
+      <c r="N57" s="5" t="n">
         <v>46191</v>
       </c>
       <c r="O57" t="inlineStr">
@@ -3808,9 +3955,14 @@
       <c r="P57" t="n">
         <v>508708</v>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Sidoarjo</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="4" t="n">
         <v>46191.61712962963</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3861,7 +4013,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N58" s="3" t="n">
+      <c r="N58" s="5" t="n">
         <v>46191</v>
       </c>
       <c r="O58" t="inlineStr">
@@ -3872,9 +4024,14 @@
       <c r="P58" t="n">
         <v>912443</v>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Sidoarjo</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="4" t="n">
         <v>46194.44393518518</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3920,12 +4077,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N59" s="3" t="n">
+      <c r="N59" s="5" t="n">
         <v>46194</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="4" t="n">
         <v>46194.35638888889</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3971,12 +4128,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N60" s="3" t="n">
+      <c r="N60" s="5" t="n">
         <v>46194</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="4" t="n">
         <v>46195.69295138889</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -4022,12 +4179,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="N61" s="5" t="n">
         <v>46195</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="4" t="n">
         <v>46204.56767361111</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -4088,7 +4245,7 @@
           <t>https://drive.google.com/open?id=Ovvb0aTZOIOoWtHSkDHPZBeBeabWlUsXk</t>
         </is>
       </c>
-      <c r="N62" s="3" t="n">
+      <c r="N62" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="O62" t="inlineStr">
@@ -4099,9 +4256,14 @@
       <c r="P62" t="n">
         <v>179324</v>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Balikpapan</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="4" t="n">
         <v>46207.35052083333</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -4157,12 +4319,12 @@
           <t>https://drive.google.com/open?id=eE0yoLujewZNnYDOZzLmdvMpVMBILmu8z</t>
         </is>
       </c>
-      <c r="N63" s="3" t="n">
+      <c r="N63" s="5" t="n">
         <v>46207</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="4" t="n">
         <v>46209.61313657407</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -4213,7 +4375,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N64" s="3" t="n">
+      <c r="N64" s="5" t="n">
         <v>46209</v>
       </c>
       <c r="O64" t="inlineStr">
@@ -4224,9 +4386,14 @@
       <c r="P64" t="n">
         <v>271684</v>
       </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Jambi</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="4" t="n">
         <v>46209.34006944444</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -4272,7 +4439,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N65" s="3" t="n">
+      <c r="N65" s="5" t="n">
         <v>46209</v>
       </c>
       <c r="O65" t="inlineStr">
@@ -4283,9 +4450,14 @@
       <c r="P65" t="n">
         <v>159442</v>
       </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Gresik</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="4" t="n">
         <v>46213.44850694444</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -4341,7 +4513,7 @@
           <t>https://drive.google.com/open?id=THCXb5zVvAKBgOy2VvEBBAqoIlmSlSft1</t>
         </is>
       </c>
-      <c r="N66" s="3" t="n">
+      <c r="N66" s="5" t="n">
         <v>46213</v>
       </c>
       <c r="O66" t="inlineStr">
@@ -4352,9 +4524,14 @@
       <c r="P66" t="n">
         <v>783275</v>
       </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Cilegon</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="4" t="n">
         <v>46213.55920138889</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -4410,12 +4587,12 @@
           <t>https://drive.google.com/open?id=ftmLSJ8pEITJEQwdzqlieCyREJqYu-Sxx</t>
         </is>
       </c>
-      <c r="N67" s="3" t="n">
+      <c r="N67" s="5" t="n">
         <v>46213</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="4" t="n">
         <v>46214.37626157407</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -4461,12 +4638,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N68" s="3" t="n">
+      <c r="N68" s="5" t="n">
         <v>46214</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="4" t="n">
         <v>46215.36107638889</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -4522,12 +4699,12 @@
           <t>https://drive.google.com/open?id=b4K4lOMVcBoVsEJZePqDQcShhNgApmEeJ</t>
         </is>
       </c>
-      <c r="N69" s="3" t="n">
+      <c r="N69" s="5" t="n">
         <v>46215</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="4" t="n">
         <v>46219.46849537037</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -4583,7 +4760,7 @@
           <t>https://drive.google.com/open?id=KYBdRPBxW5F-57jICsWi2BA6ObqGX1W_a</t>
         </is>
       </c>
-      <c r="N70" s="3" t="n">
+      <c r="N70" s="5" t="n">
         <v>46219</v>
       </c>
       <c r="O70" t="inlineStr">
@@ -4594,9 +4771,14 @@
       <c r="P70" t="n">
         <v>623952</v>
       </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Cikarang</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="4" t="n">
         <v>46220.69427083333</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -4652,7 +4834,7 @@
           <t>https://drive.google.com/open?id=PsB6DE_FoyHqlm262HyhiEfeb-ZEsCRLc</t>
         </is>
       </c>
-      <c r="N71" s="3" t="n">
+      <c r="N71" s="5" t="n">
         <v>46220</v>
       </c>
       <c r="O71" t="inlineStr">
@@ -4663,9 +4845,14 @@
       <c r="P71" t="n">
         <v>500741</v>
       </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Jambi</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="4" t="n">
         <v>46222.37211805556</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -4721,12 +4908,12 @@
           <t>https://drive.google.com/open?id=9ZbTDnmhyLLy0V948dsFkf5uXXdAFzYnF</t>
         </is>
       </c>
-      <c r="N72" s="3" t="n">
+      <c r="N72" s="5" t="n">
         <v>46222</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="4" t="n">
         <v>46224.38337962963</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -4782,12 +4969,12 @@
           <t>https://drive.google.com/open?id=o8K2rEYsyXHI_Ex6FYLgZPpAHlZG7VgUv</t>
         </is>
       </c>
-      <c r="N73" s="3" t="n">
+      <c r="N73" s="5" t="n">
         <v>46224</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="4" t="n">
         <v>46227.5191550926</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -4833,7 +5020,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N74" s="3" t="n">
+      <c r="N74" s="5" t="n">
         <v>46227</v>
       </c>
       <c r="O74" t="inlineStr">
@@ -4844,9 +5031,14 @@
       <c r="P74" t="n">
         <v>807707</v>
       </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Cilegon</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="4" t="n">
         <v>46230.55454861111</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -4892,12 +5084,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N75" s="3" t="n">
+      <c r="N75" s="5" t="n">
         <v>46230</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="4" t="n">
         <v>46236.6292824074</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -4943,7 +5135,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N76" s="3" t="n">
+      <c r="N76" s="5" t="n">
         <v>46236</v>
       </c>
       <c r="O76" t="inlineStr">
@@ -4954,9 +5146,14 @@
       <c r="P76" t="n">
         <v>733644</v>
       </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Medan</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="4" t="n">
         <v>46237.5871412037</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -5002,7 +5199,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N77" s="3" t="n">
+      <c r="N77" s="5" t="n">
         <v>46237</v>
       </c>
       <c r="O77" t="inlineStr">
@@ -5013,9 +5210,14 @@
       <c r="P77" t="n">
         <v>689431</v>
       </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Sidoarjo</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="4" t="n">
         <v>46238.68083333333</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -5061,12 +5263,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N78" s="3" t="n">
+      <c r="N78" s="5" t="n">
         <v>46238</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="4" t="n">
         <v>46239.55582175926</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -5112,12 +5314,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N79" s="3" t="n">
+      <c r="N79" s="5" t="n">
         <v>46239</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="4" t="n">
         <v>46244.34115740741</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -5163,7 +5365,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N80" s="3" t="n">
+      <c r="N80" s="5" t="n">
         <v>46244</v>
       </c>
       <c r="O80" t="inlineStr">
@@ -5174,9 +5376,14 @@
       <c r="P80" t="n">
         <v>972321</v>
       </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Denpasar</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="4" t="n">
         <v>46247.52298611111</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -5222,12 +5429,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N81" s="3" t="n">
+      <c r="N81" s="5" t="n">
         <v>46247</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="4" t="n">
         <v>46248.70733796297</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -5273,7 +5480,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N82" s="3" t="n">
+      <c r="N82" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="O82" t="inlineStr">
@@ -5284,9 +5491,14 @@
       <c r="P82" t="n">
         <v>313748</v>
       </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Makassar</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="4" t="n">
         <v>46251.36403935185</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -5342,7 +5554,7 @@
           <t>https://drive.google.com/open?id=gBkq_cuaPJB01TU4MzANx-2dQMGJQKuaN</t>
         </is>
       </c>
-      <c r="N83" s="3" t="n">
+      <c r="N83" s="5" t="n">
         <v>46251</v>
       </c>
       <c r="O83" t="inlineStr">
@@ -5353,9 +5565,14 @@
       <c r="P83" t="n">
         <v>659010</v>
       </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Cilegon</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="4" t="n">
         <v>46251.43386574074</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -5401,12 +5618,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N84" s="3" t="n">
+      <c r="N84" s="5" t="n">
         <v>46251</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="4" t="n">
         <v>46255.40290509259</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -5462,12 +5679,12 @@
           <t>https://drive.google.com/open?id=IOCatJ-BODUmtqClmKW2qbysjZWTv48W7</t>
         </is>
       </c>
-      <c r="N85" s="3" t="n">
+      <c r="N85" s="5" t="n">
         <v>46255</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="4" t="n">
         <v>46266.61733796296</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -5523,7 +5740,7 @@
           <t>https://drive.google.com/open?id=f-nlQtHk1dRDeJDToGoqnVq9oqkzdZnwf</t>
         </is>
       </c>
-      <c r="N86" s="3" t="n">
+      <c r="N86" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="O86" t="inlineStr">
@@ -5534,9 +5751,14 @@
       <c r="P86" t="n">
         <v>316728</v>
       </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Denpasar</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="4" t="n">
         <v>46268.33732638889</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -5592,12 +5814,12 @@
           <t>https://drive.google.com/open?id=TogWNKWWu4UYTVM2vZoXUkGDyyrUV2_Ak</t>
         </is>
       </c>
-      <c r="N87" s="3" t="n">
+      <c r="N87" s="5" t="n">
         <v>46268</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="4" t="n">
         <v>46274.56534722223</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -5643,7 +5865,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N88" s="3" t="n">
+      <c r="N88" s="5" t="n">
         <v>46274</v>
       </c>
       <c r="O88" t="inlineStr">
@@ -5654,9 +5876,14 @@
       <c r="P88" t="n">
         <v>857664</v>
       </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Lampung</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="4" t="n">
         <v>46275.57375</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -5702,7 +5929,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N89" s="3" t="n">
+      <c r="N89" s="5" t="n">
         <v>46275</v>
       </c>
       <c r="O89" t="inlineStr">
@@ -5713,9 +5940,14 @@
       <c r="P89" t="n">
         <v>737841</v>
       </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Gresik</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="4" t="n">
         <v>46277.5249537037</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -5761,7 +5993,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N90" s="3" t="n">
+      <c r="N90" s="5" t="n">
         <v>46277</v>
       </c>
       <c r="O90" t="inlineStr">
@@ -5772,9 +6004,14 @@
       <c r="P90" t="n">
         <v>638070</v>
       </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Denpasar</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="4" t="n">
         <v>46277.37034722222</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -5820,12 +6057,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N91" s="3" t="n">
+      <c r="N91" s="5" t="n">
         <v>46277</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="4" t="n">
         <v>46279.35072916667</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -5871,7 +6108,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N92" s="3" t="n">
+      <c r="N92" s="5" t="n">
         <v>46279</v>
       </c>
       <c r="O92" t="inlineStr">
@@ -5882,9 +6119,14 @@
       <c r="P92" t="n">
         <v>183079</v>
       </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Lampung</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="4" t="n">
         <v>46279.54971064815</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -5930,7 +6172,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N93" s="3" t="n">
+      <c r="N93" s="5" t="n">
         <v>46279</v>
       </c>
       <c r="O93" t="inlineStr">
@@ -5941,9 +6183,14 @@
       <c r="P93" t="n">
         <v>754490</v>
       </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Gresik</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="4" t="n">
         <v>46279.57023148148</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -5989,12 +6236,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N94" s="3" t="n">
+      <c r="N94" s="5" t="n">
         <v>46279</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="4" t="n">
         <v>46280.42630787037</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -6045,12 +6292,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N95" s="3" t="n">
+      <c r="N95" s="5" t="n">
         <v>46280</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="4" t="n">
         <v>46282.42446759259</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -6096,12 +6343,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N96" s="3" t="n">
+      <c r="N96" s="5" t="n">
         <v>46282</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="4" t="n">
         <v>46284.52944444444</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -6147,12 +6394,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="N97" s="3" t="n">
+      <c r="N97" s="5" t="n">
         <v>46284</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="4" t="n">
         <v>46291.58128472222</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -6208,7 +6455,7 @@
           <t>https://drive.google.com/open?id=QdkMlDo71PJjNuKVz19eBpRhFacjc-3QK</t>
         </is>
       </c>
-      <c r="N98" s="3" t="n">
+      <c r="N98" s="5" t="n">
         <v>46291</v>
       </c>
       <c r="O98" t="inlineStr">
@@ -6219,9 +6466,14 @@
       <c r="P98" t="n">
         <v>145365</v>
       </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="4" t="n">
         <v>46296.70535879629</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -6277,7 +6529,7 @@
           <t>https://drive.google.com/open?id=2z3mz2zRbGkNZnLiFfTS-yEHkTBXBdpJ0</t>
         </is>
       </c>
-      <c r="N99" s="3" t="n">
+      <c r="N99" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="O99" t="inlineStr">
@@ -6288,9 +6540,14 @@
       <c r="P99" t="n">
         <v>598231</v>
       </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Makassar</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="4" t="n">
         <v>46296.34556712963</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -6346,7 +6603,7 @@
           <t>https://drive.google.com/open?id=zp8XGcCjK9Arj5QGleLyILaTZwqjwakJo</t>
         </is>
       </c>
-      <c r="N100" s="3" t="n">
+      <c r="N100" s="5" t="n">
         <v>46296</v>
       </c>
     </row>
